--- a/InputData/elec/BCoESC/BAU Cost of Electricity Sector Capital.xlsx
+++ b/InputData/elec/BCoESC/BAU Cost of Electricity Sector Capital.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BCoESC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\BCoESC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307B0864-CA46-473C-847F-BBBACC99C132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C6479F-E270-4D80-98DB-AE12679A443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{C8F9D547-902B-4E49-8BA2-E23B0A2DC1A9}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -28,7 +31,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,179 +38,179 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Lazard</t>
+  </si>
+  <si>
+    <t>Lazard's Levelized Cost of Energy Analysis - Version 15.0</t>
+  </si>
+  <si>
+    <t>https://www.lazard.com/media/451905/lazards-levelized-cost-of-energy-version-150-vf.pdf</t>
+  </si>
+  <si>
+    <t>Page 2, first footnote (preceeding footnote 1)</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>This variable expresses the financing cost of capital construction in the electricity sector.</t>
+  </si>
+  <si>
+    <t>For debt-based financing, it should be the interest rate on the debt.</t>
+  </si>
+  <si>
+    <t>For equity-based financing, it should be the share of equity in the project given to the financier.</t>
+  </si>
+  <si>
+    <t>Projects are often a mixture of debt-based and equity-based financing.  In that case, use a</t>
+  </si>
+  <si>
+    <t>weighted average.</t>
+  </si>
+  <si>
+    <t>Debt-based financing</t>
+  </si>
+  <si>
+    <t>Equity-based financing</t>
+  </si>
+  <si>
+    <t>Cost of capital by financing mode</t>
+  </si>
+  <si>
+    <t>Weighted average cost of capital</t>
+  </si>
+  <si>
+    <t>Share of financing by mode</t>
+  </si>
+  <si>
+    <t>cost of financing</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (% of project cost)</t>
+  </si>
+  <si>
+    <t>Since the EPS works in real (inflation-adjusted) currency units, and interest rates are set by</t>
+  </si>
+  <si>
+    <t>banks and financial firms in nominal terms (factoring in their expectations of future inflation),</t>
+  </si>
+  <si>
+    <t>we need to adjust published interest rates by subtracting out the share that represents</t>
+  </si>
+  <si>
+    <t>inflation (i.e., the payment they demand just to keep up with inflation).</t>
+  </si>
+  <si>
+    <t>Inflation Adjustment</t>
+  </si>
+  <si>
+    <t>Data from Lazard</t>
+  </si>
+  <si>
+    <t>Future Inflation Estimate</t>
+  </si>
+  <si>
+    <t>U.S. Treasury Bond 30-Year Rate (Yield)</t>
+  </si>
+  <si>
+    <t>U.S. Treasury Inflation-Protected Security 30-Year Rate (Yield)</t>
+  </si>
+  <si>
+    <t>Estimated 30-Year Inflation Rate</t>
+  </si>
+  <si>
+    <t>as of 9/26/2022</t>
+  </si>
+  <si>
+    <t>Inflation-Adjusted Cost of Capital</t>
+  </si>
+  <si>
+    <t>Weighted average cost of capital minus expected inflation rate</t>
+  </si>
+  <si>
+    <t>Cost of Capital for Electricity Sector Projects</t>
+  </si>
+  <si>
+    <t>Projected Future Inflation Rate</t>
+  </si>
+  <si>
+    <t>Bloomberg</t>
+  </si>
+  <si>
+    <t>United States Rates &amp; Bonds</t>
+  </si>
+  <si>
+    <t>https://www.bloomberg.com/markets/rates-bonds/government-bonds/us</t>
+  </si>
+  <si>
+    <t>Compare 30-year treasury bond yield to 30-year treasury inflation-protected security (TIPS) yield</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>other electricity sector investments</t>
+  </si>
   <si>
     <t>BAU BCoESC Cost of Electricity Sector Capital for Power Plants</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
     <t>BAU BCoESC Cost of Electricity Sector Capital for Other Electricity Sector Investments</t>
   </si>
   <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>Cost of Capital for Electricity Sector Projects</t>
-  </si>
-  <si>
-    <t>Lazard</t>
-  </si>
-  <si>
-    <t>Lazard's Levelized Cost of Energy Analysis - Version 15.0</t>
-  </si>
-  <si>
-    <t>https://www.lazard.com/media/451905/lazards-levelized-cost-of-energy-version-150-vf.pdf</t>
-  </si>
-  <si>
-    <t>Page 2, first footnote (preceeding footnote 1)</t>
-  </si>
-  <si>
-    <t>Projected Future Inflation Rate</t>
-  </si>
-  <si>
-    <t>Bloomberg</t>
-  </si>
-  <si>
-    <t>United States Rates &amp; Bonds</t>
-  </si>
-  <si>
-    <t>https://www.bloomberg.com/markets/rates-bonds/government-bonds/us</t>
-  </si>
-  <si>
-    <t>Compare 30-year treasury bond yield to 30-year treasury inflation-protected security (TIPS) yield</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>This variable expresses the financing cost of capital construction in the electricity sector.</t>
-  </si>
-  <si>
-    <t>For debt-based financing, it should be the interest rate on the debt.</t>
-  </si>
-  <si>
-    <t>For equity-based financing, it should be the share of equity in the project given to the financier.</t>
-  </si>
-  <si>
-    <t>Projects are often a mixture of debt-based and equity-based financing.  In that case, use a</t>
-  </si>
-  <si>
-    <t>weighted average.</t>
-  </si>
-  <si>
-    <t>Inflation Adjustment</t>
-  </si>
-  <si>
-    <t>Since the EPS works in real (inflation-adjusted) currency units, and interest rates are set by</t>
-  </si>
-  <si>
-    <t>banks and financial firms in nominal terms (factoring in their expectations of future inflation),</t>
-  </si>
-  <si>
-    <t>we need to adjust published interest rates by subtracting out the share that represents</t>
-  </si>
-  <si>
-    <t>inflation (i.e., the payment they demand just to keep up with inflation).</t>
-  </si>
-  <si>
-    <t>Data from Lazard</t>
-  </si>
-  <si>
-    <t>Debt-based financing</t>
-  </si>
-  <si>
-    <t>Equity-based financing</t>
-  </si>
-  <si>
-    <t>Share of financing by mode</t>
-  </si>
-  <si>
-    <t>Cost of capital by financing mode</t>
-  </si>
-  <si>
-    <t>Weighted average cost of capital</t>
-  </si>
-  <si>
-    <t>Future Inflation Estimate</t>
-  </si>
-  <si>
-    <t>U.S. Treasury Bond 30-Year Rate (Yield)</t>
-  </si>
-  <si>
-    <t>as of 9/26/2022</t>
-  </si>
-  <si>
-    <t>U.S. Treasury Inflation-Protected Security 30-Year Rate (Yield)</t>
-  </si>
-  <si>
-    <t>Estimated 30-Year Inflation Rate</t>
-  </si>
-  <si>
-    <t>Inflation-Adjusted Cost of Capital</t>
-  </si>
-  <si>
-    <t>Weighted average cost of capital minus expected inflation rate</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (% of project cost)</t>
-  </si>
-  <si>
-    <t>cost of financing</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>solar PV</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas peaker</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
-  </si>
-  <si>
     <t>hard coal w CCS</t>
   </si>
   <si>
@@ -228,9 +230,6 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
-  </si>
-  <si>
-    <t>other electricity sector investments</t>
   </si>
 </sst>
 </file>
@@ -314,8 +313,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -335,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -651,7 +650,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F0629E-7DF7-4E6A-B1DA-78D3050B5FAD}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -660,15 +659,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -676,15 +672,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -694,27 +690,27 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -724,87 +720,87 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{867DFE11-7AC9-4394-8F96-3B3AEC2E1E67}"/>
+    <hyperlink ref="B15" r:id="rId2" xr:uid="{2E89D36F-FC27-4D19-93B8-60E068C81CDC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0493C6E0-B904-42AD-8628-915D37F837B5}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -814,22 +810,22 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4">
         <v>0.6</v>
@@ -840,7 +836,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4">
         <v>0.08</v>
@@ -851,7 +847,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B7" s="13">
         <f>SUMPRODUCT(B4:C4,B5:C5)</f>
@@ -860,36 +856,36 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B12" s="11">
         <v>3.7400000000000003E-2</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B13" s="11">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1">
         <f>B12-B13</f>
@@ -898,14 +894,14 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B20" s="12">
         <f>B7-B15</f>
@@ -918,7 +914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0D2C3E-FEFB-4F66-9667-31E7FEED72E5}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -931,15 +927,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <f>Data!$B$20</f>
@@ -948,7 +944,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <f>Data!$B$20</f>
@@ -957,7 +953,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <f>Data!$B$20</f>
@@ -966,7 +962,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <f>Data!$B$20</f>
@@ -975,7 +971,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <f>Data!$B$20</f>
@@ -984,7 +980,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <f>Data!$B$20</f>
@@ -993,7 +989,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <f>Data!$B$20</f>
@@ -1002,7 +998,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <f>Data!$B$20</f>
@@ -1011,7 +1007,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <f>Data!$B$20</f>
@@ -1020,7 +1016,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <f>Data!$B$20</f>
@@ -1029,7 +1025,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <f>Data!$B$20</f>
@@ -1038,7 +1034,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <f>Data!$B$20</f>
@@ -1047,7 +1043,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B14">
         <f>Data!$B$20</f>
@@ -1056,7 +1052,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <f>Data!$B$20</f>
@@ -1065,7 +1061,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <f>Data!$B$20</f>
@@ -1074,7 +1070,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <f>Data!$B$20</f>
@@ -1083,7 +1079,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <f>Data!$B$20</f>
@@ -1159,7 +1155,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B388480-FC75-4BF5-B02C-3AC172D606B8}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -1172,15 +1168,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <f>Data!$B$20</f>
